--- a/pds_admin_WB/Backend/Backend/Result_Sheet.xlsx
+++ b/pds_admin_WB/Backend/Backend/Result_Sheet.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="32">
   <si>
     <t>Scenario</t>
   </si>
@@ -68,6 +68,48 @@
   </si>
   <si>
     <t>Distance</t>
+  </si>
+  <si>
+    <t>Optimized</t>
+  </si>
+  <si>
+    <t>Wholesale</t>
+  </si>
+  <si>
+    <t>West Bengal</t>
+  </si>
+  <si>
+    <t>Alipurduar</t>
+  </si>
+  <si>
+    <t>AJOY NATH YADAV</t>
+  </si>
+  <si>
+    <t>FPS</t>
+  </si>
+  <si>
+    <t>Abc</t>
+  </si>
+  <si>
+    <t>bcd</t>
+  </si>
+  <si>
+    <t>cde</t>
+  </si>
+  <si>
+    <t>def</t>
+  </si>
+  <si>
+    <t>Atta</t>
+  </si>
+  <si>
+    <t>RR</t>
+  </si>
+  <si>
+    <t>PR</t>
+  </si>
+  <si>
+    <t>Wheat</t>
   </si>
 </sst>
 </file>
@@ -425,7 +467,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R1"/>
+  <dimension ref="A1:R17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:18">
@@ -484,6 +526,902 @@
         <v>17</v>
       </c>
     </row>
+    <row r="2" spans="1:18">
+      <c r="A2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2">
+        <v>3</v>
+      </c>
+      <c r="F2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G2">
+        <v>22.573481</v>
+      </c>
+      <c r="H2">
+        <v>88.23092200000001</v>
+      </c>
+      <c r="I2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J2">
+        <v>12</v>
+      </c>
+      <c r="K2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M2" t="s">
+        <v>21</v>
+      </c>
+      <c r="N2">
+        <v>11</v>
+      </c>
+      <c r="O2">
+        <v>10</v>
+      </c>
+      <c r="P2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q2">
+        <v>5</v>
+      </c>
+      <c r="R2">
+        <v>2424.4762</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18">
+      <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3">
+        <v>3</v>
+      </c>
+      <c r="F3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3">
+        <v>22.573481</v>
+      </c>
+      <c r="H3">
+        <v>88.23092200000001</v>
+      </c>
+      <c r="I3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="K3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N3">
+        <v>11</v>
+      </c>
+      <c r="O3">
+        <v>10</v>
+      </c>
+      <c r="P3" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q3">
+        <v>5</v>
+      </c>
+      <c r="R3">
+        <v>2424.4762</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18">
+      <c r="A4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4">
+        <v>3</v>
+      </c>
+      <c r="F4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4">
+        <v>22.573481</v>
+      </c>
+      <c r="H4">
+        <v>88.23092200000001</v>
+      </c>
+      <c r="I4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J4">
+        <v>3</v>
+      </c>
+      <c r="K4" t="s">
+        <v>26</v>
+      </c>
+      <c r="L4" t="s">
+        <v>20</v>
+      </c>
+      <c r="M4" t="s">
+        <v>21</v>
+      </c>
+      <c r="N4">
+        <v>11</v>
+      </c>
+      <c r="O4">
+        <v>10</v>
+      </c>
+      <c r="P4" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q4">
+        <v>5</v>
+      </c>
+      <c r="R4">
+        <v>2424.4762</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18">
+      <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5">
+        <v>3</v>
+      </c>
+      <c r="F5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G5">
+        <v>22.573481</v>
+      </c>
+      <c r="H5">
+        <v>88.23092200000001</v>
+      </c>
+      <c r="I5" t="s">
+        <v>23</v>
+      </c>
+      <c r="J5">
+        <v>4</v>
+      </c>
+      <c r="K5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L5" t="s">
+        <v>20</v>
+      </c>
+      <c r="M5" t="s">
+        <v>21</v>
+      </c>
+      <c r="N5">
+        <v>11</v>
+      </c>
+      <c r="O5">
+        <v>10</v>
+      </c>
+      <c r="P5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q5">
+        <v>5</v>
+      </c>
+      <c r="R5">
+        <v>2424.4762</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6">
+        <v>3</v>
+      </c>
+      <c r="F6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6">
+        <v>22.573481</v>
+      </c>
+      <c r="H6">
+        <v>88.23092200000001</v>
+      </c>
+      <c r="I6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J6">
+        <v>12</v>
+      </c>
+      <c r="K6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M6" t="s">
+        <v>21</v>
+      </c>
+      <c r="N6">
+        <v>11</v>
+      </c>
+      <c r="O6">
+        <v>10</v>
+      </c>
+      <c r="P6" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q6">
+        <v>7</v>
+      </c>
+      <c r="R6">
+        <v>2424.4762</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7">
+        <v>3</v>
+      </c>
+      <c r="F7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7">
+        <v>22.573481</v>
+      </c>
+      <c r="H7">
+        <v>88.23092200000001</v>
+      </c>
+      <c r="I7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J7">
+        <v>2</v>
+      </c>
+      <c r="K7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L7" t="s">
+        <v>20</v>
+      </c>
+      <c r="M7" t="s">
+        <v>21</v>
+      </c>
+      <c r="N7">
+        <v>11</v>
+      </c>
+      <c r="O7">
+        <v>10</v>
+      </c>
+      <c r="P7" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q7">
+        <v>6</v>
+      </c>
+      <c r="R7">
+        <v>2424.4762</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18">
+      <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8">
+        <v>3</v>
+      </c>
+      <c r="F8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8">
+        <v>22.573481</v>
+      </c>
+      <c r="H8">
+        <v>88.23092200000001</v>
+      </c>
+      <c r="I8" t="s">
+        <v>23</v>
+      </c>
+      <c r="J8">
+        <v>3</v>
+      </c>
+      <c r="K8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L8" t="s">
+        <v>20</v>
+      </c>
+      <c r="M8" t="s">
+        <v>21</v>
+      </c>
+      <c r="N8">
+        <v>11</v>
+      </c>
+      <c r="O8">
+        <v>10</v>
+      </c>
+      <c r="P8" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q8">
+        <v>6</v>
+      </c>
+      <c r="R8">
+        <v>2424.4762</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18">
+      <c r="A9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9">
+        <v>3</v>
+      </c>
+      <c r="F9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9">
+        <v>22.573481</v>
+      </c>
+      <c r="H9">
+        <v>88.23092200000001</v>
+      </c>
+      <c r="I9" t="s">
+        <v>23</v>
+      </c>
+      <c r="J9">
+        <v>4</v>
+      </c>
+      <c r="K9" t="s">
+        <v>27</v>
+      </c>
+      <c r="L9" t="s">
+        <v>20</v>
+      </c>
+      <c r="M9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N9">
+        <v>11</v>
+      </c>
+      <c r="O9">
+        <v>10</v>
+      </c>
+      <c r="P9" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q9">
+        <v>6</v>
+      </c>
+      <c r="R9">
+        <v>2424.4762</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10">
+        <v>3</v>
+      </c>
+      <c r="F10" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10">
+        <v>22.573481</v>
+      </c>
+      <c r="H10">
+        <v>88.23092200000001</v>
+      </c>
+      <c r="I10" t="s">
+        <v>23</v>
+      </c>
+      <c r="J10">
+        <v>12</v>
+      </c>
+      <c r="K10" t="s">
+        <v>24</v>
+      </c>
+      <c r="L10" t="s">
+        <v>20</v>
+      </c>
+      <c r="M10" t="s">
+        <v>21</v>
+      </c>
+      <c r="N10">
+        <v>11</v>
+      </c>
+      <c r="O10">
+        <v>10</v>
+      </c>
+      <c r="P10" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q10">
+        <v>24</v>
+      </c>
+      <c r="R10">
+        <v>2424.4762</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18">
+      <c r="A11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11">
+        <v>3</v>
+      </c>
+      <c r="F11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11">
+        <v>22.573481</v>
+      </c>
+      <c r="H11">
+        <v>88.23092200000001</v>
+      </c>
+      <c r="I11" t="s">
+        <v>23</v>
+      </c>
+      <c r="J11">
+        <v>2</v>
+      </c>
+      <c r="K11" t="s">
+        <v>25</v>
+      </c>
+      <c r="L11" t="s">
+        <v>20</v>
+      </c>
+      <c r="M11" t="s">
+        <v>21</v>
+      </c>
+      <c r="N11">
+        <v>11</v>
+      </c>
+      <c r="O11">
+        <v>10</v>
+      </c>
+      <c r="P11" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q11">
+        <v>24</v>
+      </c>
+      <c r="R11">
+        <v>2424.4762</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18">
+      <c r="A12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12" t="s">
+        <v>21</v>
+      </c>
+      <c r="E12">
+        <v>3</v>
+      </c>
+      <c r="F12" t="s">
+        <v>22</v>
+      </c>
+      <c r="G12">
+        <v>22.573481</v>
+      </c>
+      <c r="H12">
+        <v>88.23092200000001</v>
+      </c>
+      <c r="I12" t="s">
+        <v>23</v>
+      </c>
+      <c r="J12">
+        <v>3</v>
+      </c>
+      <c r="K12" t="s">
+        <v>26</v>
+      </c>
+      <c r="L12" t="s">
+        <v>20</v>
+      </c>
+      <c r="M12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N12">
+        <v>11</v>
+      </c>
+      <c r="O12">
+        <v>10</v>
+      </c>
+      <c r="P12" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q12">
+        <v>24</v>
+      </c>
+      <c r="R12">
+        <v>2424.4762</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18">
+      <c r="A13" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13" t="s">
+        <v>21</v>
+      </c>
+      <c r="E13">
+        <v>3</v>
+      </c>
+      <c r="F13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G13">
+        <v>22.573481</v>
+      </c>
+      <c r="H13">
+        <v>88.23092200000001</v>
+      </c>
+      <c r="I13" t="s">
+        <v>23</v>
+      </c>
+      <c r="J13">
+        <v>4</v>
+      </c>
+      <c r="K13" t="s">
+        <v>27</v>
+      </c>
+      <c r="L13" t="s">
+        <v>20</v>
+      </c>
+      <c r="M13" t="s">
+        <v>21</v>
+      </c>
+      <c r="N13">
+        <v>11</v>
+      </c>
+      <c r="O13">
+        <v>10</v>
+      </c>
+      <c r="P13" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q13">
+        <v>24</v>
+      </c>
+      <c r="R13">
+        <v>2424.4762</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18">
+      <c r="A14" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" t="s">
+        <v>21</v>
+      </c>
+      <c r="E14">
+        <v>3</v>
+      </c>
+      <c r="F14" t="s">
+        <v>22</v>
+      </c>
+      <c r="G14">
+        <v>22.573481</v>
+      </c>
+      <c r="H14">
+        <v>88.23092200000001</v>
+      </c>
+      <c r="I14" t="s">
+        <v>23</v>
+      </c>
+      <c r="J14">
+        <v>12</v>
+      </c>
+      <c r="K14" t="s">
+        <v>24</v>
+      </c>
+      <c r="L14" t="s">
+        <v>20</v>
+      </c>
+      <c r="M14" t="s">
+        <v>21</v>
+      </c>
+      <c r="N14">
+        <v>11</v>
+      </c>
+      <c r="O14">
+        <v>10</v>
+      </c>
+      <c r="P14" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q14">
+        <v>4</v>
+      </c>
+      <c r="R14">
+        <v>2424.4762</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18">
+      <c r="A15" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" t="s">
+        <v>21</v>
+      </c>
+      <c r="E15">
+        <v>3</v>
+      </c>
+      <c r="F15" t="s">
+        <v>22</v>
+      </c>
+      <c r="G15">
+        <v>22.573481</v>
+      </c>
+      <c r="H15">
+        <v>88.23092200000001</v>
+      </c>
+      <c r="I15" t="s">
+        <v>23</v>
+      </c>
+      <c r="J15">
+        <v>2</v>
+      </c>
+      <c r="K15" t="s">
+        <v>25</v>
+      </c>
+      <c r="L15" t="s">
+        <v>20</v>
+      </c>
+      <c r="M15" t="s">
+        <v>21</v>
+      </c>
+      <c r="N15">
+        <v>11</v>
+      </c>
+      <c r="O15">
+        <v>10</v>
+      </c>
+      <c r="P15" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q15">
+        <v>4</v>
+      </c>
+      <c r="R15">
+        <v>2424.4762</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18">
+      <c r="A16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" t="s">
+        <v>21</v>
+      </c>
+      <c r="E16">
+        <v>3</v>
+      </c>
+      <c r="F16" t="s">
+        <v>22</v>
+      </c>
+      <c r="G16">
+        <v>22.573481</v>
+      </c>
+      <c r="H16">
+        <v>88.23092200000001</v>
+      </c>
+      <c r="I16" t="s">
+        <v>23</v>
+      </c>
+      <c r="J16">
+        <v>3</v>
+      </c>
+      <c r="K16" t="s">
+        <v>26</v>
+      </c>
+      <c r="L16" t="s">
+        <v>20</v>
+      </c>
+      <c r="M16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N16">
+        <v>11</v>
+      </c>
+      <c r="O16">
+        <v>10</v>
+      </c>
+      <c r="P16" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q16">
+        <v>4</v>
+      </c>
+      <c r="R16">
+        <v>2424.4762</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18">
+      <c r="A17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" t="s">
+        <v>21</v>
+      </c>
+      <c r="E17">
+        <v>3</v>
+      </c>
+      <c r="F17" t="s">
+        <v>22</v>
+      </c>
+      <c r="G17">
+        <v>22.573481</v>
+      </c>
+      <c r="H17">
+        <v>88.23092200000001</v>
+      </c>
+      <c r="I17" t="s">
+        <v>23</v>
+      </c>
+      <c r="J17">
+        <v>4</v>
+      </c>
+      <c r="K17" t="s">
+        <v>27</v>
+      </c>
+      <c r="L17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M17" t="s">
+        <v>21</v>
+      </c>
+      <c r="N17">
+        <v>11</v>
+      </c>
+      <c r="O17">
+        <v>10</v>
+      </c>
+      <c r="P17" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q17">
+        <v>4</v>
+      </c>
+      <c r="R17">
+        <v>2424.4762</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/pds_admin_WB/Backend/Backend/Result_Sheet.xlsx
+++ b/pds_admin_WB/Backend/Backend/Result_Sheet.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="33">
   <si>
     <t>Scenario</t>
   </si>
@@ -82,22 +82,25 @@
     <t>Alipurduar</t>
   </si>
   <si>
-    <t>AJOY NATH YADAV</t>
+    <t>MS SOVA RANI MOULICK SONS</t>
+  </si>
+  <si>
+    <t>Ms Radha Distributor</t>
   </si>
   <si>
     <t>FPS</t>
   </si>
   <si>
-    <t>Abc</t>
-  </si>
-  <si>
-    <t>bcd</t>
-  </si>
-  <si>
-    <t>cde</t>
-  </si>
-  <si>
-    <t>def</t>
+    <t xml:space="preserve"> M/S MANOJIT SAHA</t>
+  </si>
+  <si>
+    <t>ADHIR BASUMATA</t>
+  </si>
+  <si>
+    <t>ABHIJIT  SARKAR</t>
+  </si>
+  <si>
+    <t>ABUL HOSSAIN</t>
   </si>
   <si>
     <t>Atta</t>
@@ -540,25 +543,25 @@
         <v>21</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F2" t="s">
         <v>22</v>
       </c>
       <c r="G2">
-        <v>22.573481</v>
+        <v>26.516597</v>
       </c>
       <c r="H2">
-        <v>88.23092200000001</v>
+        <v>89.533654</v>
       </c>
       <c r="I2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J2">
         <v>12</v>
       </c>
       <c r="K2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L2" t="s">
         <v>20</v>
@@ -567,19 +570,19 @@
         <v>21</v>
       </c>
       <c r="N2">
-        <v>11</v>
+        <v>26.443843</v>
       </c>
       <c r="O2">
-        <v>10</v>
+        <v>89.85445</v>
       </c>
       <c r="P2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q2">
         <v>5</v>
       </c>
       <c r="R2">
-        <v>2424.4762</v>
+        <v>46.3755</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -596,25 +599,25 @@
         <v>21</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F3" t="s">
         <v>22</v>
       </c>
       <c r="G3">
-        <v>22.573481</v>
+        <v>26.516597</v>
       </c>
       <c r="H3">
-        <v>88.23092200000001</v>
+        <v>89.533654</v>
       </c>
       <c r="I3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L3" t="s">
         <v>20</v>
@@ -623,19 +626,19 @@
         <v>21</v>
       </c>
       <c r="N3">
-        <v>11</v>
+        <v>26.664284</v>
       </c>
       <c r="O3">
-        <v>10</v>
+        <v>89.417867</v>
       </c>
       <c r="P3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q3">
         <v>5</v>
       </c>
       <c r="R3">
-        <v>2424.4762</v>
+        <v>26.4851</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -652,25 +655,25 @@
         <v>21</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G4">
-        <v>22.573481</v>
+        <v>26.480239</v>
       </c>
       <c r="H4">
-        <v>88.23092200000001</v>
+        <v>89.508205</v>
       </c>
       <c r="I4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L4" t="s">
         <v>20</v>
@@ -679,19 +682,19 @@
         <v>21</v>
       </c>
       <c r="N4">
-        <v>11</v>
+        <v>26.535997</v>
       </c>
       <c r="O4">
-        <v>10</v>
+        <v>89.18503200000001</v>
       </c>
       <c r="P4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q4">
         <v>5</v>
       </c>
       <c r="R4">
-        <v>2424.4762</v>
+        <v>36.8104</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -708,25 +711,25 @@
         <v>21</v>
       </c>
       <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5">
+        <v>26.480239</v>
+      </c>
+      <c r="H5">
+        <v>89.508205</v>
+      </c>
+      <c r="I5" t="s">
+        <v>24</v>
+      </c>
+      <c r="J5">
         <v>3</v>
       </c>
-      <c r="F5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G5">
-        <v>22.573481</v>
-      </c>
-      <c r="H5">
-        <v>88.23092200000001</v>
-      </c>
-      <c r="I5" t="s">
-        <v>23</v>
-      </c>
-      <c r="J5">
-        <v>4</v>
-      </c>
       <c r="K5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L5" t="s">
         <v>20</v>
@@ -735,19 +738,19 @@
         <v>21</v>
       </c>
       <c r="N5">
-        <v>11</v>
+        <v>26.57048</v>
       </c>
       <c r="O5">
-        <v>10</v>
+        <v>89.23535800000001</v>
       </c>
       <c r="P5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q5">
         <v>5</v>
       </c>
       <c r="R5">
-        <v>2424.4762</v>
+        <v>39.8951</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -764,25 +767,25 @@
         <v>21</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F6" t="s">
         <v>22</v>
       </c>
       <c r="G6">
-        <v>22.573481</v>
+        <v>26.516597</v>
       </c>
       <c r="H6">
-        <v>88.23092200000001</v>
+        <v>89.533654</v>
       </c>
       <c r="I6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J6">
         <v>12</v>
       </c>
       <c r="K6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L6" t="s">
         <v>20</v>
@@ -791,19 +794,19 @@
         <v>21</v>
       </c>
       <c r="N6">
-        <v>11</v>
+        <v>26.443843</v>
       </c>
       <c r="O6">
-        <v>10</v>
+        <v>89.85445</v>
       </c>
       <c r="P6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Q6">
         <v>7</v>
       </c>
       <c r="R6">
-        <v>2424.4762</v>
+        <v>46.3755</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -820,25 +823,25 @@
         <v>21</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F7" t="s">
         <v>22</v>
       </c>
       <c r="G7">
-        <v>22.573481</v>
+        <v>26.516597</v>
       </c>
       <c r="H7">
-        <v>88.23092200000001</v>
+        <v>89.533654</v>
       </c>
       <c r="I7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J7">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L7" t="s">
         <v>20</v>
@@ -847,19 +850,19 @@
         <v>21</v>
       </c>
       <c r="N7">
-        <v>11</v>
+        <v>26.664284</v>
       </c>
       <c r="O7">
-        <v>10</v>
+        <v>89.417867</v>
       </c>
       <c r="P7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Q7">
         <v>6</v>
       </c>
       <c r="R7">
-        <v>2424.4762</v>
+        <v>26.4851</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -876,25 +879,25 @@
         <v>21</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G8">
-        <v>22.573481</v>
+        <v>26.480239</v>
       </c>
       <c r="H8">
-        <v>88.23092200000001</v>
+        <v>89.508205</v>
       </c>
       <c r="I8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L8" t="s">
         <v>20</v>
@@ -903,19 +906,19 @@
         <v>21</v>
       </c>
       <c r="N8">
-        <v>11</v>
+        <v>26.535997</v>
       </c>
       <c r="O8">
-        <v>10</v>
+        <v>89.18503200000001</v>
       </c>
       <c r="P8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Q8">
         <v>6</v>
       </c>
       <c r="R8">
-        <v>2424.4762</v>
+        <v>36.8104</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -932,25 +935,25 @@
         <v>21</v>
       </c>
       <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9" t="s">
+        <v>23</v>
+      </c>
+      <c r="G9">
+        <v>26.480239</v>
+      </c>
+      <c r="H9">
+        <v>89.508205</v>
+      </c>
+      <c r="I9" t="s">
+        <v>24</v>
+      </c>
+      <c r="J9">
         <v>3</v>
       </c>
-      <c r="F9" t="s">
-        <v>22</v>
-      </c>
-      <c r="G9">
-        <v>22.573481</v>
-      </c>
-      <c r="H9">
-        <v>88.23092200000001</v>
-      </c>
-      <c r="I9" t="s">
-        <v>23</v>
-      </c>
-      <c r="J9">
-        <v>4</v>
-      </c>
       <c r="K9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L9" t="s">
         <v>20</v>
@@ -959,19 +962,19 @@
         <v>21</v>
       </c>
       <c r="N9">
-        <v>11</v>
+        <v>26.57048</v>
       </c>
       <c r="O9">
-        <v>10</v>
+        <v>89.23535800000001</v>
       </c>
       <c r="P9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Q9">
         <v>6</v>
       </c>
       <c r="R9">
-        <v>2424.4762</v>
+        <v>39.8951</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -988,25 +991,25 @@
         <v>21</v>
       </c>
       <c r="E10">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F10" t="s">
         <v>22</v>
       </c>
       <c r="G10">
-        <v>22.573481</v>
+        <v>26.516597</v>
       </c>
       <c r="H10">
-        <v>88.23092200000001</v>
+        <v>89.533654</v>
       </c>
       <c r="I10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J10">
         <v>12</v>
       </c>
       <c r="K10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L10" t="s">
         <v>20</v>
@@ -1015,19 +1018,19 @@
         <v>21</v>
       </c>
       <c r="N10">
-        <v>11</v>
+        <v>26.443843</v>
       </c>
       <c r="O10">
-        <v>10</v>
+        <v>89.85445</v>
       </c>
       <c r="P10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="Q10">
         <v>24</v>
       </c>
       <c r="R10">
-        <v>2424.4762</v>
+        <v>46.3755</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1044,25 +1047,25 @@
         <v>21</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F11" t="s">
         <v>22</v>
       </c>
       <c r="G11">
-        <v>22.573481</v>
+        <v>26.516597</v>
       </c>
       <c r="H11">
-        <v>88.23092200000001</v>
+        <v>89.533654</v>
       </c>
       <c r="I11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J11">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L11" t="s">
         <v>20</v>
@@ -1071,19 +1074,19 @@
         <v>21</v>
       </c>
       <c r="N11">
-        <v>11</v>
+        <v>26.664284</v>
       </c>
       <c r="O11">
-        <v>10</v>
+        <v>89.417867</v>
       </c>
       <c r="P11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="Q11">
         <v>24</v>
       </c>
       <c r="R11">
-        <v>2424.4762</v>
+        <v>26.4851</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1100,25 +1103,25 @@
         <v>21</v>
       </c>
       <c r="E12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G12">
-        <v>22.573481</v>
+        <v>26.480239</v>
       </c>
       <c r="H12">
-        <v>88.23092200000001</v>
+        <v>89.508205</v>
       </c>
       <c r="I12" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L12" t="s">
         <v>20</v>
@@ -1127,19 +1130,19 @@
         <v>21</v>
       </c>
       <c r="N12">
-        <v>11</v>
+        <v>26.535997</v>
       </c>
       <c r="O12">
-        <v>10</v>
+        <v>89.18503200000001</v>
       </c>
       <c r="P12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="Q12">
         <v>24</v>
       </c>
       <c r="R12">
-        <v>2424.4762</v>
+        <v>36.8104</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1156,25 +1159,25 @@
         <v>21</v>
       </c>
       <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13" t="s">
+        <v>23</v>
+      </c>
+      <c r="G13">
+        <v>26.480239</v>
+      </c>
+      <c r="H13">
+        <v>89.508205</v>
+      </c>
+      <c r="I13" t="s">
+        <v>24</v>
+      </c>
+      <c r="J13">
         <v>3</v>
       </c>
-      <c r="F13" t="s">
-        <v>22</v>
-      </c>
-      <c r="G13">
-        <v>22.573481</v>
-      </c>
-      <c r="H13">
-        <v>88.23092200000001</v>
-      </c>
-      <c r="I13" t="s">
-        <v>23</v>
-      </c>
-      <c r="J13">
-        <v>4</v>
-      </c>
       <c r="K13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L13" t="s">
         <v>20</v>
@@ -1183,19 +1186,19 @@
         <v>21</v>
       </c>
       <c r="N13">
-        <v>11</v>
+        <v>26.57048</v>
       </c>
       <c r="O13">
-        <v>10</v>
+        <v>89.23535800000001</v>
       </c>
       <c r="P13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="Q13">
         <v>24</v>
       </c>
       <c r="R13">
-        <v>2424.4762</v>
+        <v>39.8951</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -1212,25 +1215,25 @@
         <v>21</v>
       </c>
       <c r="E14">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F14" t="s">
         <v>22</v>
       </c>
       <c r="G14">
-        <v>22.573481</v>
+        <v>26.516597</v>
       </c>
       <c r="H14">
-        <v>88.23092200000001</v>
+        <v>89.533654</v>
       </c>
       <c r="I14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J14">
         <v>12</v>
       </c>
       <c r="K14" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L14" t="s">
         <v>20</v>
@@ -1239,19 +1242,19 @@
         <v>21</v>
       </c>
       <c r="N14">
-        <v>11</v>
+        <v>26.443843</v>
       </c>
       <c r="O14">
-        <v>10</v>
+        <v>89.85445</v>
       </c>
       <c r="P14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Q14">
         <v>4</v>
       </c>
       <c r="R14">
-        <v>2424.4762</v>
+        <v>46.3755</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -1268,25 +1271,25 @@
         <v>21</v>
       </c>
       <c r="E15">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F15" t="s">
         <v>22</v>
       </c>
       <c r="G15">
-        <v>22.573481</v>
+        <v>26.516597</v>
       </c>
       <c r="H15">
-        <v>88.23092200000001</v>
+        <v>89.533654</v>
       </c>
       <c r="I15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L15" t="s">
         <v>20</v>
@@ -1295,19 +1298,19 @@
         <v>21</v>
       </c>
       <c r="N15">
-        <v>11</v>
+        <v>26.664284</v>
       </c>
       <c r="O15">
-        <v>10</v>
+        <v>89.417867</v>
       </c>
       <c r="P15" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Q15">
         <v>4</v>
       </c>
       <c r="R15">
-        <v>2424.4762</v>
+        <v>26.4851</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -1324,25 +1327,25 @@
         <v>21</v>
       </c>
       <c r="E16">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G16">
-        <v>22.573481</v>
+        <v>26.480239</v>
       </c>
       <c r="H16">
-        <v>88.23092200000001</v>
+        <v>89.508205</v>
       </c>
       <c r="I16" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L16" t="s">
         <v>20</v>
@@ -1351,19 +1354,19 @@
         <v>21</v>
       </c>
       <c r="N16">
-        <v>11</v>
+        <v>26.535997</v>
       </c>
       <c r="O16">
-        <v>10</v>
+        <v>89.18503200000001</v>
       </c>
       <c r="P16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Q16">
         <v>4</v>
       </c>
       <c r="R16">
-        <v>2424.4762</v>
+        <v>36.8104</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -1380,25 +1383,25 @@
         <v>21</v>
       </c>
       <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="F17" t="s">
+        <v>23</v>
+      </c>
+      <c r="G17">
+        <v>26.480239</v>
+      </c>
+      <c r="H17">
+        <v>89.508205</v>
+      </c>
+      <c r="I17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J17">
         <v>3</v>
       </c>
-      <c r="F17" t="s">
-        <v>22</v>
-      </c>
-      <c r="G17">
-        <v>22.573481</v>
-      </c>
-      <c r="H17">
-        <v>88.23092200000001</v>
-      </c>
-      <c r="I17" t="s">
-        <v>23</v>
-      </c>
-      <c r="J17">
-        <v>4</v>
-      </c>
       <c r="K17" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L17" t="s">
         <v>20</v>
@@ -1407,19 +1410,19 @@
         <v>21</v>
       </c>
       <c r="N17">
-        <v>11</v>
+        <v>26.57048</v>
       </c>
       <c r="O17">
-        <v>10</v>
+        <v>89.23535800000001</v>
       </c>
       <c r="P17" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Q17">
         <v>4</v>
       </c>
       <c r="R17">
-        <v>2424.4762</v>
+        <v>39.8951</v>
       </c>
     </row>
   </sheetData>
